--- a/test-case.xlsx
+++ b/test-case.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\belajarqa\test\qa-myshopify-testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70042A7-E5F2-486C-AFCA-DB26AF5172A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8760D7E9-78F8-4D53-92FF-CB6517AA646B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Format Tes Case" sheetId="2" r:id="rId1"/>
@@ -1869,21 +1869,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D274D2-58D0-437D-B35C-8CD097725DFB}">
   <dimension ref="A1:N64"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="16.6328125" customWidth="1"/>
-    <col min="3" max="3" width="18.90625" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" customWidth="1"/>
-    <col min="5" max="5" width="21.1796875" customWidth="1"/>
-    <col min="6" max="6" width="29.81640625" customWidth="1"/>
-    <col min="7" max="7" width="20.7265625" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" customWidth="1"/>
-    <col min="9" max="9" width="22.6328125" customWidth="1"/>
-    <col min="10" max="10" width="23.08984375" customWidth="1"/>
-    <col min="11" max="11" width="23.81640625" customWidth="1"/>
-    <col min="12" max="13" width="12.54296875" customWidth="1"/>
-    <col min="14" max="14" width="19.1796875" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" customWidth="1"/>
+    <col min="6" max="6" width="29.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="23.109375" customWidth="1"/>
+    <col min="11" max="11" width="23.77734375" customWidth="1"/>
+    <col min="12" max="13" width="12.5546875" customWidth="1"/>
+    <col min="14" max="14" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1893,14 +1893,14 @@
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
     </row>
-    <row r="2" spans="1:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="30.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
         <v>209</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
     </row>
-    <row r="3" spans="1:14" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="47" t="s">
         <v>0</v>
       </c>
@@ -1918,7 +1918,7 @@
       <c r="M3" s="47"/>
       <c r="N3" s="47"/>
     </row>
-    <row r="4" spans="1:14" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="47"/>
       <c r="B4" s="47"/>
       <c r="C4" s="47"/>
@@ -1934,7 +1934,7 @@
       <c r="M4" s="47"/>
       <c r="N4" s="47"/>
     </row>
-    <row r="5" spans="1:14" ht="31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>38</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="26.4" x14ac:dyDescent="0.25">
       <c r="G7" s="3"/>
       <c r="H7" s="4">
         <v>2</v>
@@ -2031,7 +2031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="79.2" x14ac:dyDescent="0.25">
       <c r="F8" s="29" t="s">
         <v>81</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="G9" s="3"/>
       <c r="H9" s="4">
         <v>4</v>
@@ -2070,7 +2070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>35</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="200" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="211.2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>36</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>70</v>
       </c>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>71</v>
       </c>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="M14" s="21"/>
     </row>
-    <row r="15" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="66" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>72</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>73</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>110</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
         <v>49</v>
       </c>
@@ -2397,7 +2397,7 @@
       <c r="M18" s="48"/>
       <c r="N18" s="48"/>
     </row>
-    <row r="19" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>39</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2455,7 +2455,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2481,7 +2481,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2504,7 +2504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>50</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="214" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="214.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>53</v>
       </c>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="N25" s="38"/>
     </row>
-    <row r="26" spans="1:14" ht="194" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="193.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
         <v>62</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>170</v>
       </c>
       <c r="L27" s="20" t="s">
-        <v>12</v>
+        <v>198</v>
       </c>
       <c r="M27" s="27" t="s">
         <v>199</v>
@@ -2710,7 +2710,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="175" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="184.8" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
         <v>116</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="49" t="s">
         <v>120</v>
       </c>
@@ -2772,7 +2772,7 @@
       <c r="M29" s="50"/>
       <c r="N29" s="50"/>
     </row>
-    <row r="30" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
         <v>121</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H32" s="28">
         <v>3</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="H33" s="28">
         <v>4</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="29.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="29.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H34" s="28">
         <v>5</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="H36" s="28">
         <v>7</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="129.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="129.44999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
         <v>143</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
         <v>151</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A40" s="27" t="s">
         <v>154</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="66" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
         <v>184</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A42" s="27" t="s">
         <v>195</v>
       </c>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="N42" s="36"/>
     </row>
-    <row r="43" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
         <v>196</v>
       </c>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N43" s="36"/>
     </row>
-    <row r="44" spans="1:14" ht="36.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="45" t="s">
         <v>210</v>
       </c>
@@ -3180,7 +3180,7 @@
       <c r="M44" s="46"/>
       <c r="N44" s="46"/>
     </row>
-    <row r="45" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
         <v>212</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="66" x14ac:dyDescent="0.25">
       <c r="A46" s="27" t="s">
         <v>228</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
         <v>232</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
         <v>237</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
         <v>248</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A50" s="27" t="s">
         <v>254</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
         <v>265</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="66" x14ac:dyDescent="0.25">
       <c r="A52" s="27" t="s">
         <v>273</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="66" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
         <v>279</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A54" s="27" t="s">
         <v>284</v>
       </c>
@@ -3559,7 +3559,7 @@
       <c r="M54" s="27"/>
       <c r="N54" s="41"/>
     </row>
-    <row r="55" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
         <v>297</v>
       </c>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="M55" s="27"/>
     </row>
-    <row r="56" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A56" s="27" t="s">
         <v>305</v>
       </c>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="M56" s="27"/>
     </row>
-    <row r="57" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
         <v>315</v>
       </c>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="M57" s="27"/>
     </row>
-    <row r="58" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A58" s="27" t="s">
         <v>322</v>
       </c>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="M58" s="27"/>
     </row>
-    <row r="59" spans="1:14" ht="187.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="198" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
         <v>323</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="187.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="211.2" x14ac:dyDescent="0.25">
       <c r="A60" s="27" t="s">
         <v>337</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
         <v>344</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
         <v>345</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="53" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="52.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="44"/>
       <c r="B63" s="44"/>
       <c r="C63" s="44"/>
@@ -3964,9 +3964,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EDE8B49-D087-4812-BF0F-D99D1473E5CD}">
   <dimension ref="D2:H8"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="4:8" ht="31" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>12</v>
       </c>
